--- a/artfynd/A 32160-2024 artfynd.xlsx
+++ b/artfynd/A 32160-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,7 +680,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119161406</v>
+        <v>54268159</v>
       </c>
       <c r="B2" t="n">
         <v>79394</v>
@@ -709,19 +709,21 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Renhagaberget, Renhagaberget, Ång</t>
+          <t>Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660860</v>
+        <v>660922</v>
       </c>
       <c r="R2" t="n">
-        <v>6982807</v>
+        <v>6982841</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +747,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2015-06-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2015-06-16</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På flera träd</t>
+          <t>På flera granar i myrkant</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,28 +768,33 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Torrgran i myrkant</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119161406</t>
+          <t>https://artportalen.se/Sighting/54268159</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119161897</v>
+        <v>119161406</v>
       </c>
       <c r="B3" t="n">
         <v>79394</v>
@@ -822,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660894</v>
+        <v>660860</v>
       </c>
       <c r="R3" t="n">
-        <v>6982783</v>
+        <v>6982807</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,6 +865,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På flera träd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,13 +895,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119161897</t>
+          <t>https://artportalen.se/Sighting/119161406</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119162214</v>
+        <v>119161897</v>
       </c>
       <c r="B4" t="n">
         <v>79394</v>
@@ -924,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>660884</v>
+        <v>660894</v>
       </c>
       <c r="R4" t="n">
-        <v>6982778</v>
+        <v>6982783</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,38 +997,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119162214</t>
+          <t>https://artportalen.se/Sighting/119161897</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119166929</v>
+        <v>119162214</v>
       </c>
       <c r="B5" t="n">
-        <v>93189</v>
+        <v>79394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>637</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,13 +1038,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>660582</v>
+        <v>660884</v>
       </c>
       <c r="R5" t="n">
-        <v>6982828</v>
+        <v>6982778</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,38 +1099,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119166929</t>
+          <t>https://artportalen.se/Sighting/119162214</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119167181</v>
+        <v>119162467</v>
       </c>
       <c r="B6" t="n">
-        <v>93189</v>
+        <v>79394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>637</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>660440</v>
+        <v>660925</v>
       </c>
       <c r="R6" t="n">
-        <v>6982949</v>
+        <v>6982858</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,38 +1201,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119167181</t>
+          <t>https://artportalen.se/Sighting/119162467</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119160131</v>
+        <v>119162643</v>
       </c>
       <c r="B7" t="n">
-        <v>91930</v>
+        <v>79394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>637</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1242,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>660691</v>
+        <v>660919</v>
       </c>
       <c r="R7" t="n">
-        <v>6982864</v>
+        <v>6982877</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1291,16 +1303,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119160131</t>
+          <t>https://artportalen.se/Sighting/119162643</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119162294</v>
+        <v>119162694</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>79394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,21 +1320,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>637</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,13 +1344,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>660875</v>
+        <v>660923</v>
       </c>
       <c r="R8" t="n">
-        <v>6982755</v>
+        <v>6982894</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1368,11 +1380,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,16 +1405,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119162294</t>
+          <t>https://artportalen.se/Sighting/119162694</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119162345</v>
+        <v>119162756</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>79394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,21 +1422,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>637</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>660858</v>
+        <v>660916</v>
       </c>
       <c r="R9" t="n">
-        <v>6982733</v>
+        <v>6982898</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1477,11 +1484,6 @@
           <t>2024-08-16</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1505,38 +1507,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119162345</t>
+          <t>https://artportalen.se/Sighting/119162756</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119160385</v>
+        <v>119166929</v>
       </c>
       <c r="B10" t="n">
-        <v>57950</v>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,13 +1548,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>660766</v>
+        <v>660582</v>
       </c>
       <c r="R10" t="n">
-        <v>6982850</v>
+        <v>6982828</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1582,11 +1584,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,59 +1609,54 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119160385</t>
+          <t>https://artportalen.se/Sighting/119166929</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119167008</v>
+        <v>119167181</v>
       </c>
       <c r="B11" t="n">
-        <v>57141</v>
+        <v>93189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Renhagaberget, Renhagaberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>660474</v>
+        <v>660440</v>
       </c>
       <c r="R11" t="n">
-        <v>6982852</v>
+        <v>6982949</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1719,38 +1711,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119167008</t>
+          <t>https://artportalen.se/Sighting/119167181</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119167231</v>
+        <v>119160131</v>
       </c>
       <c r="B12" t="n">
-        <v>57141</v>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>660432</v>
+        <v>660691</v>
       </c>
       <c r="R12" t="n">
-        <v>6982963</v>
+        <v>6982864</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,7 +1777,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Ullånger</t>
+          <t>Skog</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1796,11 +1788,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Tjäderspillning under tjäderbetad tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,59 +1813,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119167231</t>
+          <t>https://artportalen.se/Sighting/119160131</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119162319</v>
+        <v>119162294</v>
       </c>
       <c r="B13" t="n">
-        <v>58114</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Renhagaberget, Renhagaberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>660870</v>
+        <v>660875</v>
       </c>
       <c r="R13" t="n">
-        <v>6982760</v>
+        <v>6982755</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1908,6 +1890,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1933,38 +1920,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119162319</t>
+          <t>https://artportalen.se/Sighting/119162294</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119160498</v>
+        <v>119162345</v>
       </c>
       <c r="B14" t="n">
-        <v>99035</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1961,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>660769</v>
+        <v>660858</v>
       </c>
       <c r="R14" t="n">
-        <v>6982842</v>
+        <v>6982733</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2012,6 +1999,11 @@
           <t>2024-08-16</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2034,6 +2026,643 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119162345</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>119160385</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Renhagaberget, Renhagaberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>660766</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6982850</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119160385</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>119162928</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Renhagaberget, Renhagaberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>660953</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6982861</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119162928</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>119167008</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Renhagaberget, Renhagaberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>660474</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6982852</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119167008</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>119167231</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Renhagaberget, Renhagaberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>660432</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6982963</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ullånger</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Tjäderspillning under tjäderbetad tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119167231</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>119162319</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Renhagaberget, Renhagaberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>660870</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6982760</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119162319</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>119160498</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Renhagaberget, Renhagaberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>660769</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6982842</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119160498</t>
         </is>
@@ -2054,6 +2683,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
